--- a/table/Datas/#Cosmetic.xlsx
+++ b/table/Datas/#Cosmetic.xlsx
@@ -659,12 +659,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>primitive</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dummy/HatCubeRed</t>
+          <t>cube:#E53935:0.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>primitive</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dummy/HatCubeBlue</t>
+          <t>cube:#1E88E5:0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>prefab</t>
+          <t>primitive</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dummy/AccSphere</t>
+          <t>sphere:#FFD54F:0.15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>decal</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Face/FaceAtlas</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>decal</t>
+          <t>expression</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Face/FaceAtlasB</t>
+          <t>Cheer</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">

--- a/table/Datas/#Cosmetic.xlsx
+++ b/table/Datas/#Cosmetic.xlsx
@@ -746,6 +746,11 @@
           <t>tint</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>#3B82F6</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -860,6 +865,11 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>tint</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>#3A3450</t>
         </is>
       </c>
     </row>
